--- a/MSME/Test upload format/MSME_Update.xlsx
+++ b/MSME/Test upload format/MSME_Update.xlsx
@@ -47,7 +47,7 @@
     <t>NPAInterestAmount</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357195</t>
+    <t>CGMSMGEN2210202600357241</t>
   </si>
   <si>
     <t>Aloan04</t>
@@ -59,10 +59,10 @@
     <t>05-04-2028</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357207</t>
-  </si>
-  <si>
-    <t>Aloan16</t>
+    <t>CGMSMGEN2210202600357242</t>
+  </si>
+  <si>
+    <t>Aloan05</t>
   </si>
 </sst>
 </file>
@@ -736,10 +736,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1006,7 +1006,7 @@
   <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelRow="2" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="29" style="2" customWidth="1"/>
-    <col min="2" max="2" width="23.1047619047619" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26" style="2" customWidth="1"/>
     <col min="3" max="3" width="15.7809523809524" style="2" customWidth="1"/>
     <col min="4" max="4" width="25.4380952380952" style="3" customWidth="1"/>
     <col min="5" max="5" width="35.1047619047619" style="2" customWidth="1"/>
@@ -1038,19 +1038,19 @@
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6">
         <v>500000000</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <v>0</v>
       </c>
     </row>
@@ -1058,19 +1058,19 @@
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>100000000</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>0</v>
       </c>
     </row>
